--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>85</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>22/08 19:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>16/08 13:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>22/08 23:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>55</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>16/08 19:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>16/08 21:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>60</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>16/08 13:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>60</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>16/08 18:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>17/08 19:15</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>17/08 01:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F14" t="n">
+        <v>2.85</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>55</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>17/08 16:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>16/08 23:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F17" t="n">
+        <v>2.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>50</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>17/08 13:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F20" t="n">
+        <v>3.1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>16/08 23:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3.3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>16/08 14:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>16/08 19:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>16/08 19:15</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>65</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>17/08 17:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>55</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45885.07437285448</v>
+        <v>45885.0743728588</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,111 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+14,5%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45885.0743728588</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Las Palmas</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Las Palmas – FC AndorraLaLiga2 - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>17/08 19:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45885.13650585566</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Kashima An</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Kashima Antlers – Avispa FukuokaJ-League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>16/08 09:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+14,5%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45885.07437285448</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+13,8%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45885.13650585566</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>17/08 19:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>55</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45885.13650585566</v>
+        <v>45885.13650585648</v>
       </c>
     </row>
     <row r="28">
@@ -1625,23 +1623,111 @@
           <t>16/08 09:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>50</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+13,8%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45885.13650585648</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Godoy Cruz – Velez SarsfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>25/08 20:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>+13,8%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>45885.13650585566</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45885.18639309889</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Belgran</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CA Belgrano – Central CordobaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>25/08 22:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45885.18639309889</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>50</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45885.18639309889</v>
+        <v>45885.18639310185</v>
       </c>
     </row>
     <row r="30">
@@ -1711,23 +1709,111 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45885.18639310185</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Jeonbuk Mo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors – Daegu FCK League 1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>16/08 10:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>+18,7%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>45885.18639309889</v>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+18,5%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45885.22338860451</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 6 | SV Hemelin</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SV Hemelingen – WolfsbourgAllemagne - Coupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 6</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>16/08 13:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+16,2%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45885.22338860451</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>16/08 10:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>50</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45885.22338860451</v>
+        <v>45885.22338859954</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>16/08 13:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
+      <c r="F32" t="n">
+        <v>3.85</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,97 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45885.22338860451</v>
+        <v>45885.22338859954</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 14.5 - tirs2e équipe | Volendam –</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Volendam – AZPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>17/08 14:45</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>46,0%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+26,5%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45885.27204667822</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 26.5 - tirs | Go Ahead E</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles – Ajax AmsterdamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>17/08 10:15</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>45,7%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+25,7%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45885.27204667822</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>17/08 14:45</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.75</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45885.27204667822</v>
+        <v>45885.27204667824</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>17/08 10:15</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.75</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,142 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45885.27204667822</v>
+        <v>45885.27204667824</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 29.5 - tirs | Atletico M</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – Gremio RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 29.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>17/08 19:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>43,0%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+33,4%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45885.30586354212</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 23.5 | N.Mektic /</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>N.Mektic / R.Ram – J.Cash / L.GlasspoolATP - Cincinnati, Doubles</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 23.5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16/08 15:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+21,1%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45885.30586354212</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 11.5 - tirs2e équipe | GKS Katowi</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GKS Katowice – Arka GdyniaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>16/08 15:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>48,8%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+18,6%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45885.30586354212</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F35" t="n">
+        <v>3.1</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45885.30586354212</v>
+        <v>45885.30586354167</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>16/08 15:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>5.10</t>
-        </is>
+      <c r="F36" t="n">
+        <v>5.1</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45885.30586354212</v>
+        <v>45885.30586354167</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>16/08 15:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.43</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,187 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45885.30586354212</v>
+        <v>45885.30586354167</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 26.5 - tirs | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Botafogo – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>17/08 23:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45885.35266655538</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | La Equidad</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>La Equidad – Llaneros FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>16/08 20:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,40%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+20,0%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45885.35266655538</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Central Co</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Central Cordoba – Barracas CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>17/08 19:15</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45885.35266655538</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Arda KardzhaliLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+19,1%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45885.35266655538</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,10 +2053,8 @@
           <t>17/08 23:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F38" t="n">
+        <v>2.75</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2069,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45885.35266655538</v>
+        <v>45885.35266655093</v>
       </c>
     </row>
     <row r="39">
@@ -2098,10 +2096,8 @@
           <t>16/08 20:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>50</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2114,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45885.35266655538</v>
+        <v>45885.35266655093</v>
       </c>
     </row>
     <row r="40">
@@ -2143,10 +2139,8 @@
           <t>17/08 19:15</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>50</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2159,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45885.35266655538</v>
+        <v>45885.35266655093</v>
       </c>
     </row>
     <row r="41">
@@ -2188,10 +2182,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>50</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2204,7 +2196,97 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45885.35266655538</v>
+        <v>45885.35266655093</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs1re équipe | Go Ahead E</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles – Ajax AmsterdamPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>17/08 10:15</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+17,5%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45885.39038433559</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 12.5 - tirs1re équipe | Minnesota </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Minnesota United – Seattle SoundersÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>17/08 00:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+16,9%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45885.39038433559</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>17/08 10:15</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.95</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45885.39038433559</v>
+        <v>45885.39038434028</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>17/08 00:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.65</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,52 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45885.39038433559</v>
+        <v>45885.39038434028</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Plus que 5.5 - aces2e participant | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Terence AtmaneATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - aces2e participant</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>16/08 19:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>66,0%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+15,4%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45885.43170407554</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>16/08 19:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="F44" t="n">
+        <v>1.75</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,52 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45885.43170407554</v>
+        <v>45885.43170407407</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Rosario Ce</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Rosario Central – Deportivo RiestraLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>16/08 21:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+20,6%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45885.47042083973</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>16/08 21:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>50</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,52 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45885.47042083973</v>
+        <v>45885.4704208449</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | UTA Arad –</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UTA Arad – FC Unirea 2004 SloboziaLiga 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22/08 16:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+16,1%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45885.5292079538</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>22/08 16:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>45</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,97 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45885.5292079538</v>
+        <v>45885.52920795139</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Colorado R</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Colorado Rapids – Atlanta UnitedÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>17/08 01:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+14,6%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45885.56188408798</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Hajduk Spl</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hajduk Split – NK SlavenHNL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>17/08 19:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45885.56188408798</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>17/08 01:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F47" t="n">
+        <v>2.7</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45885.56188408798</v>
+        <v>45885.56188408565</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,52 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45885.56188408798</v>
+        <v>45885.56188408565</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Tokyo Verd</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy – Sanfrecce HiroshimaJ-League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>23/08 10:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+29,4%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45885.59654179806</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -2526,10 +2526,8 @@
           <t>23/08 10:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>60</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45885.59654179806</v>
+        <v>45885.59654179398</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,6 +2543,96 @@
         <v>45885.59654179398</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | RSV Eintra</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>RSV Eintracht Stahnsdorf 1949 – KaiserslauternCoupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>17/08 13:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+17,5%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45885.68469713534</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Volendam –</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Volendam – AZPays-Bas - Pays-Bas Eredivisie</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>17/08 14:45</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+15,3%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45885.68469713534</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -2569,10 +2569,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>60</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45885.68469713534</v>
+        <v>45885.68469712963</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>17/08 14:45</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.9</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45885.68469713534</v>
+        <v>45885.68469712963</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2629,6 +2629,51 @@
         <v>45885.68469712963</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 20.5 - tirs | Celta Vigo</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Celta Vigo – GetafeLaLiga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Moins que 20.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>17/08 15:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>44,1%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+14,6%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45885.77076709879</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,142 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45885.77076709879</v>
+        <v>45885.77076709491</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico M</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – GremioSérie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17/08 19:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+14,2%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45885.80366042545</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Plus que 12.5 - tirs1re équipe | Valence – </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Valence – Real SociedadEspagne - LaLiga</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>16/08 19:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>35,1%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+12,2%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45885.80366042545</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Colorado R</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Colorado Rapids – Atlanta UnitedÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>17/08 01:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>41,4%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+11,8%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45885.80366042545</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>55</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45885.80366042545</v>
+        <v>45885.80366042824</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>16/08 19:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3.2</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45885.80366042545</v>
+        <v>45885.80366042824</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>17/08 01:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.7</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,142 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45885.80366042545</v>
+        <v>45885.80366042824</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Maccabi Ne</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Maccabi Netanya – Hapoel Beer ShevaPremier League</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>24/08 17:15</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+33,3%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45885.84929373093</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 28.5 - tirs | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sport Recife – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 28.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>16/08 21:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>37,2%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45885.84929373093</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs2e équipe | Elche – Be</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Elche – BetisEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+11,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45885.84929373093</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>50</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45885.84929373093</v>
+        <v>45885.84929372685</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>16/08 21:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45885.84929373093</v>
+        <v>45885.84929372685</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F58" t="n">
+        <v>2.8</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45885.84929373093</v>
+        <v>45885.84929372685</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 14.5 - tirs1re équipe | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sport Recife – Sao Paulo SPBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>16/08 21:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>45,7%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+15,1%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45885.88869673728</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs2e équipe | Colorado R</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Colorado Rapids – Atlanta UnitedÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>17/08 01:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+14,3%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45885.88869673728</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>16/08 21:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
+      <c r="F59" t="n">
+        <v>2.52</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45885.88869673728</v>
+        <v>45885.88869673611</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>17/08 01:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.1</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,142 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45885.88869673728</v>
+        <v>45885.88869673611</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico N</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Atletico Nacional – Fortaleza FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>17/08 00:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+38,1%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45885.93103499201</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | ASC Otelul</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ASC Otelul Galati – CFR ClujLiga 1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>24/08 13:15</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45885.93103499201</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | SV Eintrac</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SV Eintracht 1949 – KaiserslauternAllemagne. Coupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>17/08 13:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+12,4%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45885.93103499201</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-16.xlsx
+++ b/data/valuebets_database_2025-08-16.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>17/08 00:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>60</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45885.93103499201</v>
+        <v>45885.93103498843</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>24/08 13:15</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>50</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45885.93103499201</v>
+        <v>45885.93103498843</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>70</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,142 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45885.93103499201</v>
+        <v>45885.93103498843</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Sportivo AmelianoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>23/08 19:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+27,6%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45885.97232422141</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs2e équipe | Toronto FC</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Toronto FC – Columbus CrewÉtats-Unis - États-Unis MLS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>16/08 23:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+10,8%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45885.97232422141</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Barracas C</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Barracas Central – Defensa y JusticiaLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+9,62%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45885.97232422141</v>
       </c>
     </row>
   </sheetData>
